--- a/семинар_пакет/04_приложения_и_реестры/MEDICAL_EVIDENCE.xlsx
+++ b/семинар_пакет/04_приложения_и_реестры/MEDICAL_EVIDENCE.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,1147 +461,1147 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Орган/автор, год</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Уровень</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Статус верификации</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Где используется</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>M-cloz_hagg</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Hägg S. et al. Кофеин 400–1000 мг/день: +19% AUC клозапина, −14% клиренс</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2014893/</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>M-cloz_case</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Yartsev P. et al. Тяжёлая токсичность клозапина при приёме энергетиков (600 мг кофеина/день; уровень 1796 нг/мл) — клинический случай</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8043221/</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>M-cloz_wd</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Отмена кофеина: снижение уровня клозапина на 37–47% (Carrillo 1998; обзор)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>клинический обзор</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.pharmacytimes.com/view/caffeine-and-clozapine</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>M-lithium</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Литий и диета: почки обрабатывают литий и натрий сходно; дефицит натрия/обезвоживание → рост уровня лития</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Cleveland Clinic</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://my.clevelandclinic.org/health/diseases/25207-lithium-toxicity</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>M-lithium_sp</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>StatPearls. Lithium Toxicity: риски — дегидратация, диуретики, лихорадка, потери ЖКТ</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>StatPearls</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://www.ncbi.nlm.nih.gov/books/NBK499992/</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>M-carb_gf</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Garg S.K. et al. Грейпфрутовый сок: пик карбамазепина 6,55→9,20 мкг/мл (+40%), AUC +41%</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>1998</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/9757152/</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>M-maoi_nhs</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>NHS. MAOI — диетические ограничения (тирамин): пациентский листок</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>NHS</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.torbayandsouthdevon.nhs.uk/uploads/25672.pdf?last-updated=20201119</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>M-maoi_hist</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>«Сырная реакция» на ИМАО: история открытия (Blackwell; АД 160/90→220/115)</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>исторический обзор</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2738414/</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>M-maoi_guide</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>MAOI diet and tyramine: руководство для назначающих (обновление 2022)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>prescriber’s guide</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9172554/</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>M-pillinger</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Pillinger T. et al. Мета-анализ 100 РКИ (25 952 пациента): прибавка веса на антипсихотиках от −0,23 кг (галоперидол) до +3,01 кг (клозапин) за медиану 6 нед (Lancet Psychiatry, 2020)</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/31860457/</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>M-crwg</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Мета-анализ CRWG (прибавка ≥7% за 38 нед): клозапин 76,3%, оланзапин 36,9%, рисперидон 23,0% (BJPsych Open, 2026)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.cambridge.org/core/journals/bjpsych-open/article/association-between-antipsychotic-medication-and-clinically-relevant-weight-change-metaanalysis/C2DC78D062978D7C805E0E9B99B7911F</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>M-fepwg</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Мета-анализ при первом эпизоде психоза: долгосрочно оланзапин +9,34 кг, клозапин +7,19 кг</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>мета-анализ</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5589463/</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>M-metmon</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Мониторинг метаболического риска на антипсихотиках: график (вес/ИМТ: исходно, 4/8/12 нед, 6 мес, ежегодно; глюкоза/липиды/АД: исходно, 12 нед, ежегодно)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>клинические рекомендации</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8582768/</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>M-lifestyle</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Lifestyle interventions in mental health conditions: systematic review (57 исследований; −1,42 кг)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9462072/</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>M-teasdale</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Teasdale S. et al. Nutrition/dietary interventions for SMI (MJA, 2023)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9828433/</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>M-resolve</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>RESOLVE: реалистский синтез антипсихотической прибавки веса (2025)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12531729/</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>M-dysph_prev</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Font L. et al. Дисфагия на фоне антипсихотиков: распространённость 21,9–69,5% (систематический обзор)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>систематический обзор</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10455044/</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>M-dysph_rev</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Дисфагия при шизофрении: механизмы (паркинсонизм, сухость, гиперсаливация, седация, нарушения еды) — обзор</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>обзор</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://www.frontiersin.org/journals/psychiatry/articles/10.3389/fpsyt.2024.1448623/full</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>M-dysph_dd</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Дисфагия, аспирационная пневмония и кишечная непроходимость на антипсихотиках у лиц с нарушениями развития; предупреждение FDA о запорах на клозапине (2020)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>обзор</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://www.jscimedcentral.com/public/assets/articles/psychiatry-11-1183.pdf</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>M-mortality</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Correll C. et al. Мета-анализ смертности при шизофрении: смерть на 15–20 лет раньше; пневмония RR 7,00 — высшая из естественных причин (World Psychiatry, 2022)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9077617/</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>M-mortality2</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Шведский регистр: ССЗ — ведущая причина избыточной смертности при шизофрении (MRR 2,80; смерть от ССЗ на 10 лет моложе)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>регистровое исследование</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6137375/</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>M-iddsi2017</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Cichero J.A.Y. et al. The IDDSI Framework (Dysphagia, 2017;32(2):293–314)</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>IDDSI, 2017</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/27913916/</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>M-iddsi_wu</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Wu X.S. et al. IDDSI implementation: соответствие текстур 44%→90%</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8994209/</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>M-nijs</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Nijs K. et al. Family-style mealtimes: cluster RCT (BMJ, 2006)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC1463975/</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>M-montessori</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Montessori-based interventions for dementia: systematic review (15 исследований)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10336713/</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>M-pm_rev</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Porter J. et al. Protected mealtimes: systematic review &amp; meta-analysis (Int J Nurs Stud, 2017)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/27866011/</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>M-pm_rct</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Porter J. et al. Protected Mealtimes: stepped-wedge cluster trial (2019)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5295189/</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>M-sup_hous</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Supported housing for people with SMI: systematic review &amp; meta-analysis (2022)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Frontiers in Psychiatry</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://www.frontiersin.org/journals/psychiatry/articles/10.3389/fpsyt.2022.966029/full</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>M-ebt</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Исследование «Если быть точным»: ПНИ России в цифрах — 466 интернатов (2024), 139 500 жителей, 74% недееспособных, 65% старше 45 лет (апрель 2026)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://www.forbes.ru/forbeslife/558987-s-2022-po-2024-god-cislo-psihonevrologiceskih-internatov-v-rossii-snizilos-na-13</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>M-ebt2</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Исследование «Если быть точным»: сопровождаемое проживание — 7 000 чел.; переименование ПНИ в «дома социального обслуживания» в 41 регионе (2026)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://tochno.st/materials/kak-ustroeny-pni-v-rossii-issledovanie-esli-byt-tocnym</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>верифицировано 22–23.07.2026 при подготовке клинического блока; перенесено в новый проект 23.07.2026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>см. главы 9–14 доклада (пищевое поведение, препараты, дисфагия, мониторинг)</t>
         </is>
@@ -2048,6 +2048,191 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>глава 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>M-comf_oralfeed</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Oral feeding options for people with dementia: a systematic review</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>систематический обзор (2011); PMID 21391936</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/21391936/</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>верифицировано 17.08.2026</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>раздел 12 (comfort feeding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>M-comf_jnha</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Comfort feeding in hospitalised people with dementia: a retrospective study of survival following comfort feeding recommendations</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>J Nutr Health Aging, 2024; DOI 10.1016/j.jnha.2024.100362</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jnha.2024.100362</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>верифицировано 17.08.2026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>раздел 12 (comfort feeding, выживаемость)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>M-hydr_esp</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ESPEN guideline on clinical nutrition and hydration in geriatrics</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ESPEN (Европейское общество клинического питания и метаболизма); Clin Nutr</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.espen.org/files/ESPEN-Guidelines/ESPEN_guideline_on_clincal_nutrition_and_hydration_in_geriatrics.pdf</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>верифицировано 17.08.2026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>приложение 40 (питьевой режим)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>M-hydr_palt</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Dehydration and Fluid Maintenance in the Long-Term Care Setting — клиническое руководство</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PALTmed (Общество паллиативной медицины), 2024</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://paltmed.org/sites/default/files/2024-10/Dehydration%20CPG%2008092024.pdf</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>верифицировано 17.08.2026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>приложение 40 (питьевой режим в LTC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>M-hydr_low</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Narrative Review of Low-Intake Dehydration in Older Adults</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>обзор (2021); PMC8470893</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8470893/</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>верифицировано 17.08.2026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>приложение 40 (распространённость дегидратации)</t>
         </is>
       </c>
     </row>

--- a/семинар_пакет/04_приложения_и_реестры/MEDICAL_EVIDENCE.xlsx
+++ b/семинар_пакет/04_приложения_и_реестры/MEDICAL_EVIDENCE.xlsx
@@ -2133,7 +2133,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ESPEN guideline on clinical nutrition and hydration in geriatrics</t>
+          <t>Volkert D. et al. ESPEN guideline on clinical nutrition and hydration in geriatrics ( Clin Nutr, 2019, 38(1):10–47)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.espen.org/files/ESPEN-Guidelines/ESPEN_guideline_on_clincal_nutrition_and_hydration_in_geriatrics.pdf</t>
+          <t>https://doi.org/10.1016/j.clnu.2018.05.029</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">

--- a/семинар_пакет/04_приложения_и_реестры/MEDICAL_EVIDENCE.xlsx
+++ b/семинар_пакет/04_приложения_и_реестры/MEDICAL_EVIDENCE.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2236,6 +2236,43 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>M-must_bapen</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BAPEN. MUST — Malnutrition Universal Screening Tool: 5-шаговый скрининг (ИМТ, непреднамеренная потеря &gt;5 % за 3–6 мес, острое заболевание); для домов ухода — регулярное (обычно ежемесячное) взвешивание</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BAPEN, Великобритания, 2003/2018</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.bapen.org.uk/pdfs/must/must_explan.pdf</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>проверено 18.08.2026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>глава 13.8, панель 22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
